--- a/mod_project/data_tables/balance_tutorial_text.xlsx
+++ b/mod_project/data_tables/balance_tutorial_text.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutorials" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tutorials" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,6 +501,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>max_lines</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lines of a box of a lesson or of the library</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_width</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Characters of a line: the originals reach 75 in Lesson.pck and 69 in Teaching.pck</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -755,7 +817,7 @@
         <is>
           <t>"*giggle* Don't be so timid, Fried. Examine their requirements
 in the menu and coordinate your turns to store Pep. A well-timed
-Joint Skill can pierce tough defenses and turn tides in an instant."</t>
+Joint Skill can turn the tide in an instant."</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -765,12 +827,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>checked</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>"Pierce tough defenses" is not read (see Teaching 17)</t>
+          <t>Was "pierce tough defenses": not read. Pep needed and spent: FORMULAS 13</t>
         </is>
       </c>
     </row>
@@ -1104,20 +1166,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Crafting a Sealbook permanently unlocks monster Level, HP, and
-Resistances in battle! Equip Sealbooks for stats or forge them
-onto weapons at the Blacksmith (+1 to +9) to inherit enchants.</t>
+          <t>Each Sealbook offers different enchantments. A character who
+carries one gains them as if they were on her equipment,
+so make plenty and use them to strengthen your party.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>checked</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nothing read says what a sealbook reveals in battle nor that it is forged onto a weapon from +1 to +9</t>
+          <t>Was "permanently unlocks monster Level, HP and Resistances" and "forge them onto weapons (+1 to +9)": neither is read. Read: the enchantments of a carried sealbook join the list of her pieces (0x4f7b5d)</t>
         </is>
       </c>
     </row>
@@ -1140,20 +1202,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mutant bosses drop Grand Sealbooks with 100% guarantee.
-Equipping one provides powerful passive auras that boost the
-entire party, plus summons the mutant as an autonomous ally!</t>
+          <t>Carry one Grand Sealbook at a time: its enchantment works for
+the whole party, and the mutant it holds fights beside you
+as an ally you do not command.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>checked</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The drop rate of a Grand Sealbook is not read. The party-wide enchantment and the summon are FORMULAS 16.1</t>
+          <t>Was "drop with 100% guarantee": the drop is not read. FORMULAS 16.1 and 11: one carried, its enchantment for the party, its summon in the party acting by its own script</t>
         </is>
       </c>
     </row>
@@ -1211,22 +1273,15 @@
 whose Sealbooks you have created before.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Press &lt;BUTTON_L&gt; to inspect monsters. Creating their Sealbook
-permanently reveals Max HP, ATK, DEF, and all 5 elemental
-resistances, allowing you to exploit their vulnerabilities!</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>held</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>What a sealbook reveals is not read</t>
+          <t>What a sealbook reveals is not read: the original line stays</t>
         </is>
       </c>
     </row>
@@ -1247,22 +1302,15 @@
 battle log to see who did what during battle.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>The battle log reveals crucial combat details: spell chants,
-exact status resistance checks, boss rotation shifts, and turn
-delay procs. Review it closely to refine your boss strategy!</t>
-        </is>
-      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>held</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The contents of the battle log are not read</t>
+          <t>The contents of the battle log are not read: the original line stays</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1614,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Joint skills pierce defenses and unleash devastating power!
+          <t>Joint skills unleash devastating power!
 Each joint skill can only be used once per battle, so time
 their activation carefully to break through dangerous phases.</t>
         </is>
@@ -1574,12 +1622,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>checked</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>"Pierce defenses" is not read: a joint skill goes through the magic formula with its Power (FORMULAS 15). Once per battle is the original line</t>
+          <t>Was "pierce defenses": not read (a joint skill goes through the magic formula with its Power, FORMULAS 15). Once per battle is the original line</t>
         </is>
       </c>
     </row>
@@ -1601,22 +1649,15 @@
 than to level 1.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Resetting allows reclassing and reallocating all skill points.
-You can reset to Level 1 or to intermediate class thresholds
-(Level 15 or Level 30) to freely experiment with new builds.</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>held</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>The levels a reset may stop at are not read</t>
+          <t>The levels a reset may stop at are not read: the original line stays</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_tutorial_text.xlsx
+++ b/mod_project/data_tables/balance_tutorial_text.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,7 +1061,6 @@
 allowing heavy weapon wielders to maintain tactical tempo!</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1098,7 +1097,6 @@
 and higher levels for decisive burst damage against tough foes.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1135,7 +1133,6 @@
 while Dolls act as autonomous allies on their own turns.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1171,7 +1168,6 @@
 so make plenty and use them to strengthen your party.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1207,7 +1203,6 @@
 as an ally you do not command.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1244,7 +1239,6 @@
 Summons act on their own turns and cannot be commanded.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1273,7 +1267,6 @@
 whose Sealbooks you have created before.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>held</t>
@@ -1302,7 +1295,6 @@
 battle log to see who did what during battle.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>held</t>
@@ -1339,7 +1331,6 @@
 Choosing Defend advances your turn gauge to recover sooner.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1375,7 +1366,6 @@
 One heavy hit or a high-crit skill stops a spell best.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1412,7 +1402,6 @@
 bows and magic strike any enemy row at 100% full power.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1448,7 +1437,6 @@
 so time your heaviest burst attacks accordingly!</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1484,7 +1472,6 @@
 completely immune to the status ailments of that element.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1520,7 +1507,6 @@
 to sustain deeper dungeon expeditions and rare loot.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1555,7 +1541,6 @@
 preserving that awakened power even after resetting to Level 1!</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1583,7 +1568,6 @@
           <t>Party skills grow stronger the more Awards you obtain.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>held</t>
@@ -1619,7 +1603,6 @@
 their activation carefully to break through dangerous phases.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1649,7 +1632,6 @@
 than to level 1.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>held</t>
@@ -1686,7 +1668,6 @@
 Facing higher-level monsters also grants native bonus EXP.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1722,7 +1703,6 @@
 even in zones where normal party magic is silenced.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1758,7 +1738,6 @@
 equipped with advanced techniques to support deep explorations.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1795,7 +1774,6 @@
 weapon delay tiers to master late-game tactical encounters.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1831,7 +1809,6 @@
 and Joint Skills to finish them before they overwhelm you.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1868,7 +1845,6 @@
 Chant interruption to shut down enemy magic users.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1905,7 +1881,6 @@
 resistances increase by +1 permanently, building toward Crown EX.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>checked</t>
@@ -1914,6 +1889,75 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>FORMULAS 10: a reset of 59 levels or more adds 1 (up to 5 at 98); resistances too (0x4f5f04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lesson.pck</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Talk_Scenario27.adv.bin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>"While most things in this world can be resolved with gold,
+there do exist a limited subset of problems that all the
+money in the world couldn't fix."</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>"What gold cannot buy, a nimble thief may lift from a monster:
+one of the things it would drop, and only once from each."</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>checked</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>FORMULAS 12.16: a steal that succeeds draws among the drops of the enemy (0x4504bf calls 0x558180 with its steal flag), once per enemy (0x154). Not voiced. The first two boxes of the talk are the original ones</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Lesson.pck</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Talk_Scenario27.adv.bin</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>"You'll understand when you're older... and then you'll wish
+you didn't."</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>"Most bosses, mind you, guard their pockets far too well.
+You'll understand when you try... and then wish you hadn't."</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>checked</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bit 15 of the flags of an enemy (0x4503c5): 131 of the 157 enemies that only stand in fixed battles do not have it. The end of the original box is kept as the joke of the talk</t>
         </is>
       </c>
     </row>
